--- a/docs/spec/CookPilot_기능명세서_HIPO.xlsx
+++ b/docs/spec/CookPilot_기능명세서_HIPO.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>사용자가 입력한 Gemini API Key 를 검증해 브라우저에 저장하고, 이후 요리 기능이 조회해 사용한다. 서버로 전송하지 않는다.</t>
+          <t>사용자가 입력한 Gemini API Key 를 검증해 브라우저에 저장하고, 이후 요리 기능이 조회해 사용한다. 브라우저가 Gemini API 를 직접 호출하므로 CookPilot 서버로는 전송하지 않는다. 단 FN11 상담은 서버를 거친다.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>사용자가 입력한 Gemini API Key 를 검증해 브라우저에 저장하고, 이후 요리 기능이 조회해 사용한다. 서버로 전송하지 않는다.</t>
+          <t>사용자가 입력한 Gemini API Key 를 검증해 브라우저에 저장하고, 이후 요리 기능이 조회해 사용한다. 브라우저가 Gemini API 를 직접 호출하므로 CookPilot 서버로는 전송하지 않는다. 단 FN11 상담은 서버를 거친다.</t>
         </is>
       </c>
       <c r="G4" s="16" t="inlineStr">
@@ -26392,7 +26392,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>요리 · 상담 기능이 사용하는 외부 API 인증 값. 서버로 전송하지 않는다</t>
+          <t>요리 · 상담 기능이 사용하는 외부 API 인증 값. CookPilot 서버에 저장하지 않는다 (FN11 은 요청 시에만 경유)</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
